--- a/verification/cases/roundtrip/structured_refs/init.xlsx
+++ b/verification/cases/roundtrip/structured_refs/init.xlsx
@@ -1,25 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GregWoolsey\svn\ApachePOI SVN\test-data\spreadsheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95F968F1-71AD-4428-9D38-8B1B2A568E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25050" windowHeight="10365"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formulas" sheetId="2" r:id="rId1"/>
     <sheet name="Table" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -57,7 +69,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -114,14 +126,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="\_Prime.1" displayName="\_Prime.1" ref="A1:C7" totalsRowShown="0">
-  <autoFilter ref="A1:C7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="\_Prime.1" displayName="\_Prime.1" ref="A1:C7" totalsRowShown="0">
+  <autoFilter ref="A1:C7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="5" name="calc=#*#" dataDxfId="0">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="calc=#*#" dataDxfId="0">
       <calculatedColumnFormula>\_Prime.1[[#This Row],[Number]]*\_Prime.1[[#This Row],[Number]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" name="Name"/>
-    <tableColumn id="2" name="Number"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Number"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -423,25 +435,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1">
         <f>SUM(\_Prime.1[calc='#*'#])</f>
         <v>209</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
-        <f>\_Prime.1[Name]</f>
+        <f>\_Prime.1[[#This Row],[Name]]</f>
         <v>one</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
-        <f>\_Prime.1[Name]</f>
+        <f>\_Prime.1[[#This Row],[Name]]</f>
         <v>two</v>
       </c>
     </row>
@@ -451,15 +463,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -470,7 +482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>\_Prime.1[[#This Row],[Number]]*\_Prime.1[[#This Row],[Number]]</f>
         <v>1</v>
@@ -482,7 +494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>\_Prime.1[[#This Row],[Number]]*\_Prime.1[[#This Row],[Number]]</f>
         <v>4</v>
@@ -494,7 +506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>\_Prime.1[[#This Row],[Number]]*\_Prime.1[[#This Row],[Number]]</f>
         <v>9</v>
@@ -506,7 +518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>\_Prime.1[[#This Row],[Number]]*\_Prime.1[[#This Row],[Number]]</f>
         <v>25</v>
@@ -518,7 +530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>\_Prime.1[[#This Row],[Number]]*\_Prime.1[[#This Row],[Number]]</f>
         <v>49</v>
@@ -530,7 +542,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>\_Prime.1[[#This Row],[Number]]*\_Prime.1[[#This Row],[Number]]</f>
         <v>121</v>
